--- a/artfynd/A 34087-2022 artfynd.xlsx
+++ b/artfynd/A 34087-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34087-2022 artfynd.xlsx
+++ b/artfynd/A 34087-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106231329</v>
+        <v>106231321</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337243.8033829293</v>
+        <v>337099</v>
       </c>
       <c r="R2" t="n">
-        <v>6639013.474404604</v>
+        <v>6639073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106231330</v>
+        <v>106231317</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337243.8033829293</v>
+        <v>337099</v>
       </c>
       <c r="R3" t="n">
-        <v>6639013.474404604</v>
+        <v>6639073</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +847,14 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera tallar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,16 +885,11 @@
         <v>106231336</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -950,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337103.219363977</v>
+        <v>337103</v>
       </c>
       <c r="R4" t="n">
-        <v>6638990.473166595</v>
+        <v>6638991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +953,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,6 +980,208 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106231330</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr Tippmyrens NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337243</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6639013</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Köla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106231329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr Tippmyrens NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337243</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6639013</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Köla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34087-2022 artfynd.xlsx
+++ b/artfynd/A 34087-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231336</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106231329</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>